--- a/My project/JsonConverter/ExcelFiles/Crop.xlsx
+++ b/My project/JsonConverter/ExcelFiles/Crop.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\MonsterRestaurant\My project\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD30C156-1E92-428B-8CE7-C33EBBBBBAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7E4E3A-8EEA-4AA8-A235-D377EDF6A5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19815" yWindow="3000" windowWidth="19680" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="2520" windowWidth="19680" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -233,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -258,28 +258,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -293,6 +271,39 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -517,9 +528,9 @@
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
     <col min="2" max="2" width="19.5703125" customWidth="1"/>
-    <col min="3" max="3" width="50.7109375" customWidth="1"/>
-    <col min="4" max="4" width="23.5703125" style="22" customWidth="1"/>
-    <col min="5" max="5" width="30.5703125" style="22" customWidth="1"/>
+    <col min="3" max="3" width="50.7109375" style="28" customWidth="1"/>
+    <col min="4" max="4" width="23.5703125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="30.5703125" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" customHeight="1">
@@ -527,7 +538,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="1"/>
-      <c r="C1" s="12"/>
+      <c r="C1" s="18"/>
     </row>
     <row r="2" spans="1:15" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -536,13 +547,13 @@
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="13" t="s">
         <v>11</v>
       </c>
     </row>
@@ -553,13 +564,13 @@
       <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="17" t="s">
         <v>16</v>
       </c>
     </row>
@@ -570,13 +581,13 @@
       <c r="B4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="14" t="s">
         <v>6</v>
       </c>
       <c r="F4" s="3"/>
@@ -597,13 +608,13 @@
       <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="25"/>
+      <c r="E5" s="15"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -618,9 +629,9 @@
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
       <c r="A6" s="5"/>
       <c r="B6" s="5"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -635,9 +646,9 @@
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
       <c r="A7" s="4"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -652,9 +663,9 @@
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
       <c r="A8" s="6"/>
       <c r="B8" s="6"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -669,9 +680,9 @@
     <row r="9" spans="1:15" ht="15.75" customHeight="1">
       <c r="A9" s="6"/>
       <c r="B9" s="6"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -686,9 +697,9 @@
     <row r="10" spans="1:15" ht="15.75" customHeight="1">
       <c r="A10" s="7"/>
       <c r="B10" s="7"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
@@ -703,9 +714,9 @@
     <row r="11" spans="1:15" ht="15.75" customHeight="1">
       <c r="A11" s="7"/>
       <c r="B11" s="7"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -720,9 +731,9 @@
     <row r="12" spans="1:15" ht="15.75" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
@@ -737,9 +748,9 @@
     <row r="13" spans="1:15" ht="15.75" customHeight="1">
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
@@ -754,9 +765,9 @@
     <row r="14" spans="1:15" ht="15.75" customHeight="1">
       <c r="A14" s="7"/>
       <c r="B14" s="7"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
@@ -771,9 +782,9 @@
     <row r="15" spans="1:15" ht="15.75" customHeight="1">
       <c r="A15" s="7"/>
       <c r="B15" s="7"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
@@ -788,108 +799,108 @@
     <row r="16" spans="1:15" ht="15.75" customHeight="1">
       <c r="A16" s="8"/>
       <c r="B16" s="8"/>
-      <c r="C16" s="18"/>
+      <c r="C16" s="24"/>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
-      <c r="C17" s="19"/>
+      <c r="C17" s="25"/>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1">
       <c r="A18" s="9"/>
       <c r="B18" s="9"/>
-      <c r="C18" s="19"/>
+      <c r="C18" s="25"/>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1">
       <c r="A19" s="9"/>
       <c r="B19" s="9"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1">
       <c r="A20" s="9"/>
       <c r="B20" s="9"/>
-      <c r="C20" s="19"/>
+      <c r="C20" s="25"/>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1">
       <c r="A21" s="9"/>
       <c r="B21" s="9"/>
-      <c r="C21" s="19"/>
+      <c r="C21" s="25"/>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1">
       <c r="A22" s="9"/>
       <c r="B22" s="9"/>
-      <c r="C22" s="19"/>
+      <c r="C22" s="25"/>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
-      <c r="C23" s="19"/>
+      <c r="C23" s="25"/>
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1">
       <c r="A24" s="9"/>
       <c r="B24" s="9"/>
-      <c r="C24" s="19"/>
+      <c r="C24" s="25"/>
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1">
       <c r="A25" s="9"/>
       <c r="B25" s="9"/>
-      <c r="C25" s="19"/>
-      <c r="E25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="E25" s="15"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="B26" s="10"/>
-      <c r="C26" s="20"/>
-      <c r="E26" s="25"/>
+      <c r="C26" s="26"/>
+      <c r="E26" s="15"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="10"/>
-      <c r="C27" s="20"/>
-      <c r="E27" s="25"/>
+      <c r="C27" s="26"/>
+      <c r="E27" s="15"/>
     </row>
     <row r="28" spans="1:5" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="10"/>
-      <c r="C28" s="20"/>
-      <c r="E28" s="25"/>
+      <c r="C28" s="26"/>
+      <c r="E28" s="15"/>
     </row>
     <row r="29" spans="1:5" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="10"/>
-      <c r="C29" s="20"/>
+      <c r="C29" s="26"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
-      <c r="C30" s="20"/>
+      <c r="C30" s="26"/>
     </row>
     <row r="31" spans="1:5" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="B31" s="10"/>
-      <c r="C31" s="20"/>
+      <c r="C31" s="26"/>
     </row>
     <row r="32" spans="1:5" ht="15.75" customHeight="1">
       <c r="A32" s="11"/>
       <c r="B32" s="11"/>
-      <c r="C32" s="21"/>
+      <c r="C32" s="27"/>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1">
       <c r="A33" s="11"/>
       <c r="B33" s="11"/>
-      <c r="C33" s="21"/>
+      <c r="C33" s="27"/>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1">
       <c r="A34" s="11"/>
       <c r="B34" s="11"/>
-      <c r="C34" s="21"/>
+      <c r="C34" s="27"/>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1">
       <c r="A35" s="11"/>
       <c r="B35" s="11"/>
-      <c r="C35" s="21"/>
+      <c r="C35" s="27"/>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="37" spans="1:3" ht="15.75" customHeight="1"/>

--- a/My project/JsonConverter/ExcelFiles/Crop.xlsx
+++ b/My project/JsonConverter/ExcelFiles/Crop.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\MonsterRestaurant\My project\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7E4E3A-8EEA-4AA8-A235-D377EDF6A5A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB4CE7B2-EA3A-4370-998F-E15B70C39EF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="2520" windowWidth="19680" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DNTable_Weapon" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>(name)</t>
   </si>
@@ -86,6 +86,18 @@
   </si>
   <si>
     <t>NextLevelID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CropState</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Growing</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Harvestable</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -233,7 +245,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -259,7 +271,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -304,6 +316,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -531,6 +546,7 @@
     <col min="3" max="3" width="50.7109375" style="28" customWidth="1"/>
     <col min="4" max="4" width="23.5703125" style="12" customWidth="1"/>
     <col min="5" max="5" width="30.5703125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" customHeight="1">
@@ -556,6 +572,9 @@
       <c r="E2" s="13" t="s">
         <v>11</v>
       </c>
+      <c r="F2" s="29" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
@@ -573,6 +592,9 @@
       <c r="E3" s="17" t="s">
         <v>16</v>
       </c>
+      <c r="F3" s="17" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -590,7 +612,9 @@
       <c r="E4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3"/>
+      <c r="F4" s="14" t="s">
+        <v>18</v>
+      </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -615,7 +639,9 @@
         <v>15</v>
       </c>
       <c r="E5" s="15"/>
-      <c r="F5" s="3"/>
+      <c r="F5" s="15" t="s">
+        <v>19</v>
+      </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
@@ -632,7 +658,7 @@
       <c r="C6" s="21"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
-      <c r="F6" s="3"/>
+      <c r="F6" s="15"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
@@ -649,7 +675,7 @@
       <c r="C7" s="20"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
-      <c r="F7" s="3"/>
+      <c r="F7" s="15"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
@@ -666,7 +692,7 @@
       <c r="C8" s="22"/>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
-      <c r="F8" s="3"/>
+      <c r="F8" s="15"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
@@ -683,7 +709,7 @@
       <c r="C9" s="22"/>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
-      <c r="F9" s="3"/>
+      <c r="F9" s="15"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -700,7 +726,7 @@
       <c r="C10" s="23"/>
       <c r="D10" s="15"/>
       <c r="E10" s="15"/>
-      <c r="F10" s="3"/>
+      <c r="F10" s="15"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
@@ -717,7 +743,7 @@
       <c r="C11" s="23"/>
       <c r="D11" s="15"/>
       <c r="E11" s="15"/>
-      <c r="F11" s="3"/>
+      <c r="F11" s="15"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -734,7 +760,7 @@
       <c r="C12" s="22"/>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
-      <c r="F12" s="3"/>
+      <c r="F12" s="15"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -751,7 +777,7 @@
       <c r="C13" s="20"/>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
-      <c r="F13" s="3"/>
+      <c r="F13" s="15"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -768,7 +794,7 @@
       <c r="C14" s="23"/>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
-      <c r="F14" s="3"/>
+      <c r="F14" s="15"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -785,7 +811,7 @@
       <c r="C15" s="23"/>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
-      <c r="F15" s="3"/>
+      <c r="F15" s="15"/>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
